--- a/data/demo/documents/D-09_fuel_upstream.xlsx
+++ b/data/demo/documents/D-09_fuel_upstream.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Fuel upstream statement — Sinopec fuel card</t>
+          <t>Fuel upstream statement — Valero fuel card</t>
         </is>
       </c>
     </row>
